--- a/data_extactor/batch/301_350.xlsx
+++ b/data_extactor/batch/301_350.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9AAA0-53CC-4E1F-AC17-62E30E994551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF125BA7-49ED-4156-BAD7-D16B1A8D24BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="541">
   <si>
     <t>25-1021.00</t>
   </si>
@@ -1588,6 +1588,66 @@
   </si>
   <si>
     <t>Adapt instructional techniques to the age and skill levels of students. | Advise education professionals of students' physical abilities or disabilities and the accommodations required to enhance their school performance. | Assess students' physical progress or needs. | Assist in screening or placement of students in adapted physical education programs. | Attend in-service training, workshops, or meetings to keep abreast of current practices or trends in adapted physical education. | Collaborate with other educational personnel to provide inclusive activities or programs for children with disabilities. | Communicate behavioral observations and student progress reports to students, parents, teachers, or administrators. | Establish and maintain standards of behavior to create safe, orderly, and effective environments for learning. | Evaluate the motor needs of individual students to determine their need for adapted physical education services. | Instruct students, using adapted physical education techniques, to improve physical fitness, gross motor skills, perceptual motor skills, or sports and game achievement. | Maintain inventory of instructional equipment, materials, or aids. | Maintain thorough student records to document attendance, participation, or progress, ensuring confidentiality of all records. | Prepare lesson plans in accordance with individualized education plans (IEPs) and the functional abilities or needs of students. | Provide adapted physical education services to students with intellectual disabilities, autism, traumatic brain injury, orthopedic impairments, or other disabling condition. | Provide individual or small groups of students with adapted physical education instruction that meets desired physical needs or goals. | Provide students positive feedback to encourage them and help them develop an appreciation for physical education. | Request or order physical education equipment, following standard procedures. | Review adapted physical education programs or practices to ensure compliance with government or other regulations. | Write or modify individualized education plans (IEPs) for students with intellectual or physical disabilities. | Write reports to summarize student performance, social growth, or physical development.</t>
+  </si>
+  <si>
+    <t>Criminology Professor | Ethnic Studies Professor | Gender Studies Professor | International Relations Professor | Linguistics Professor | Public Administration Professor | Social Sciences Instructor | Social Sciences Lecturer | Social Sciences Professor | Urban Studies Professor</t>
+  </si>
+  <si>
+    <t>Learning management system LMS | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software | Google Docs | Web browser software | Microsoft Outlook | Database software | Graphic presentation software | Microsoft Office software | IBM SPSS Statistics | R</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Learning Strategies | Writing | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Sociology and Anthropology | English Language | Education and Training | History and Archeology | Psychology | Law and Government | Philosophy and Theology | Communications and Media | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Sociology Teachers, Postsecondary | Political Science Teachers, Postsecondary | Psychology Teachers, Postsecondary | Economics Teachers, Postsecondary | Geography Teachers, Postsecondary | Anthropology and Archeology Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | History Teachers, Postsecondary | Philosophy and Religion Teachers, Postsecondary | Social Work Teachers, Postsecondary | Criminal Justice and Law Enforcement Teachers, Postsecondary | Education Teachers, Postsecondary | Communications Teachers, Postsecondary | Business Teachers, Postsecondary | Law Teachers, Postsecondary | Postsecondary Teachers, All Other | Sociologists | Political Scientists | Education Administrators, Postsecondary | Instructional Coordinators</t>
+  </si>
+  <si>
+    <t>Teach courses in social sciences disciplines not classified separately. | Prepare and deliver lectures, seminars, and discussion sections. | Develop course syllabi, reading lists, assignments, and assessment methods. | Evaluate and grade student coursework, examinations, and research projects. | Advise students on academic programs, research, and career options. | Conduct original research and publish findings in scholarly outlets. | Supervise undergraduate and graduate student research and theses. | Maintain office hours to provide individual instruction and guidance. | Serve on departmental, college, and university committees. | Keep current with developments in the discipline through study and conferences. | Write grant proposals to fund research and instructional programs. | Participate in curriculum development and program review activities. | Collaborate with colleagues on interdisciplinary teaching and research. | Perform administrative duties such as program coordination and student recruitment.</t>
+  </si>
+  <si>
+    <t>Adjunct Professor | Assistant Professor | Associate Professor | College Instructor | College Professor | Faculty Member | Lecturer | Postsecondary Instructor | University Professor | Visiting Professor</t>
+  </si>
+  <si>
+    <t>Learning management system LMS | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software | Google Docs | Web browser software | Microsoft Outlook | Database software | Graphic presentation software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Education and Training | English Language | Communications and Media | Computers and Electronics | Psychology | Administration and Management | Mathematics | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Business Teachers, Postsecondary | Computer Science Teachers, Postsecondary | Education Teachers, Postsecondary | Health Specialties Teachers, Postsecondary | Communications Teachers, Postsecondary | English Language and Literature Teachers, Postsecondary | Foreign Language and Literature Teachers, Postsecondary | Art, Drama, and Music Teachers, Postsecondary | Career/Technical Education Teachers, Postsecondary | Recreation and Fitness Studies Teachers, Postsecondary | Family and Consumer Sciences Teachers, Postsecondary | Library Science Teachers, Postsecondary | Social Sciences Teachers, Postsecondary, All Other | Instructional Coordinators | Education Administrators, Postsecondary | Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Self-Enrichment Teachers | Tutors | Training and Development Specialists | Educational, Guidance, and Career Counselors and Advisors</t>
+  </si>
+  <si>
+    <t>Teach postsecondary courses in subjects not classified separately. | Prepare and deliver lectures, laboratories, and studio or clinical instruction. | Develop curricula, syllabi, and instructional materials for assigned courses. | Assess student learning through assignments, examinations, and projects. | Advise and mentor students on academic and professional development. | Maintain regularly scheduled office hours for student consultation. | Conduct scholarly or applied research within the discipline. | Publish articles, books, and instructional resources. | Serve on academic committees and participate in institutional governance. | Stay current with disciplinary developments and instructional technologies. | Supervise teaching assistants, laboratory staff, and student workers. | Participate in accreditation, assessment, and program review processes. | Recruit students and represent the program at outreach events. | Collaborate with industry or community partners on applied projects.</t>
+  </si>
+  <si>
+    <t>Education and Training | Psychology | English Language | Therapy and Counseling | Customer and Personal Service | Sociology and Anthropology | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Physical Proximity | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Public Speaking | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Written Letters and Memos | Exposed to Disease or Infections</t>
+  </si>
+  <si>
+    <t>Adaptive Skills Teacher | Autism Support Teacher | Behavior Intervention Teacher | Exceptional Student Educator | Inclusion Teacher | Learning Support Teacher | Resource Room Teacher | Special Education Teacher | Special Needs Teacher | Transition Specialist</t>
+  </si>
+  <si>
+    <t>Education and Training | Psychology | English Language | Therapy and Counseling | Customer and Personal Service | Sociology and Anthropology | Computers and Electronics | Law and Government</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | E-Mail | Telephone Conversations | Spend Time Standing | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Frequency of Decision Making | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Dealing with Violent or Physically Aggressive People</t>
+  </si>
+  <si>
+    <t>Special Education Teachers, Preschool | Special Education Teachers, Kindergarten | Special Education Teachers, Elementary School | Special Education Teachers, Middle School | Special Education Teachers, Secondary School | Adapted Physical Education Specialists | Teaching Assistants, Special Education | Elementary School Teachers, Except Special Education | Middle School Teachers, Except Special and Career/Technical Education | Secondary School Teachers, Except Special and Career/Technical Education | Kindergarten Teachers, Except Special Education | Preschool Teachers, Except Special Education | Instructional Coordinators | Educational, Guidance, and Career Counselors and Advisors | School Psychologists | Speech-Language Pathologists | Occupational Therapists | Rehabilitation Counselors | Education Administrators, Kindergarten through Secondary | Tutors</t>
+  </si>
+  <si>
+    <t>Teach students with disabilities in settings not classified separately. | Develop and implement individualized education programs for assigned students. | Adapt curricula, materials, and assessments to students' abilities and needs. | Assess students' academic, functional, and behavioral skills and document progress. | Employ specialized instructional strategies and assistive technologies. | Design and implement behavior intervention plans and reinforcement systems. | Confer with parents, guardians, and multidisciplinary teams about student needs. | Coordinate services with therapists, counselors, and general education teachers. | Maintain compliance with special education laws, timelines, and documentation. | Instruct students in daily living, social, communication, and vocational skills. | Supervise and direct the work of teaching assistants and paraprofessionals. | Prepare students for transitions between grade levels, schools, or employment. | Attend eligibility meetings and contribute to placement decisions. | Participate in professional development on disabilities and instructional methods.</t>
   </si>
 </sst>
 </file>
@@ -2545,8 +2605,32 @@
       <c r="B19" t="s">
         <v>199</v>
       </c>
+      <c r="C19" t="s">
+        <v>521</v>
+      </c>
+      <c r="D19" t="s">
+        <v>522</v>
+      </c>
+      <c r="E19" t="s">
+        <v>523</v>
+      </c>
+      <c r="F19" t="s">
+        <v>524</v>
+      </c>
+      <c r="G19" t="s">
+        <v>525</v>
+      </c>
+      <c r="H19" t="s">
+        <v>526</v>
+      </c>
+      <c r="I19" t="s">
+        <v>527</v>
+      </c>
       <c r="J19" t="s">
         <v>200</v>
+      </c>
+      <c r="K19" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -3116,8 +3200,32 @@
       <c r="B36" t="s">
         <v>378</v>
       </c>
+      <c r="C36" t="s">
+        <v>529</v>
+      </c>
+      <c r="D36" t="s">
+        <v>530</v>
+      </c>
+      <c r="E36" t="s">
+        <v>523</v>
+      </c>
+      <c r="F36" t="s">
+        <v>531</v>
+      </c>
+      <c r="G36" t="s">
+        <v>525</v>
+      </c>
+      <c r="H36" t="s">
+        <v>526</v>
+      </c>
+      <c r="I36" t="s">
+        <v>532</v>
+      </c>
       <c r="J36" t="s">
         <v>379</v>
+      </c>
+      <c r="K36" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -3413,6 +3521,18 @@
       <c r="D45" t="s">
         <v>471</v>
       </c>
+      <c r="E45" t="s">
+        <v>523</v>
+      </c>
+      <c r="F45" t="s">
+        <v>534</v>
+      </c>
+      <c r="G45" t="s">
+        <v>525</v>
+      </c>
+      <c r="H45" t="s">
+        <v>535</v>
+      </c>
       <c r="I45" t="s">
         <v>472</v>
       </c>
@@ -3535,8 +3655,32 @@
       <c r="B49" t="s">
         <v>508</v>
       </c>
+      <c r="C49" t="s">
+        <v>536</v>
+      </c>
+      <c r="D49" t="s">
+        <v>530</v>
+      </c>
+      <c r="E49" t="s">
+        <v>523</v>
+      </c>
+      <c r="F49" t="s">
+        <v>537</v>
+      </c>
+      <c r="G49" t="s">
+        <v>525</v>
+      </c>
+      <c r="H49" t="s">
+        <v>538</v>
+      </c>
+      <c r="I49" t="s">
+        <v>539</v>
+      </c>
       <c r="J49" t="s">
         <v>509</v>
+      </c>
+      <c r="K49" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
